--- a/Bug_Log_Smart_Farm.xlsx
+++ b/Bug_Log_Smart_Farm.xlsx
@@ -589,7 +589,13 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>By Design — NHƯNG PHẢI GIẢI THÍCH ĐÚNG LÝ DO. Đừng nói với hội đồng đây là cơ chế chống sụt áp: chỉ cần họ bấm một van rồi hỏi lại là lộ. Lý do thật hay hơn: ESP32 nằm sau NAT nên máy chủ không gọi xuống được, thiết bị phải tự hỏi mỗi 3 giây (kiến trúc kéo). Đổi lại: không cần IP tĩnh, không phải mở cổng vào mạng nội bộ, và mất mạng thì tủ vẫn tự chạy AUTO tại chỗ. Muốn nhanh hơn thì rút ngắn chu kỳ hỏi, đánh đổi bằng lưu lượng và điện năng. Cơ chế giãn 2 giây chống sụt áp là chuyện CÓ THẬT nhưng của nút 'Kiểm tra toàn dàn' — vẫn nên khoe, chỉ là khoe đúng chỗ.</t>
+          <t>ĐÃ SỬA (không còn để By Design nữa). Độ trễ đo được giảm từ ~1830 ms xuống ~32 ms.
+Cách làm: máy chủ GIỮ yêu cầu /api/commands/pending lại (?wait=) thay vì trả mảng rỗng ngay, và trả về đúng lúc có lệnh mới vào hàng đợi.
+KHÔNG rút ngắn chu kỳ hỏi — đó là cách sai: firmware đặt setReuse(false) nên mỗi lượt hỏi mở một kết nối TLS mới, hỏi dày gấp ba là bắt tay TLS gấp ba, mà tác vụ mạng trên ESP32 chạy TUẦN TỰ nên nó sẽ giành mất chỗ của việc đẩy số đo lên.
+Mức giữ co giãn theo hạn đẩy số đo kế tiếp, nên nhịp telemetry KHÔNG bị trễ một mili giây nào (đo: 3013 ms trước và sau) và số lượt hỏi lúc rảnh giữ nguyên (0,332 → 0,330 lượt/giây). Mỗi lệnh người dùng bấm tốn thêm đúng một lượt hỏi.
+Máy chủ cũng tự co mức giữ khi có lệnh hẹn giờ sắp tới hạn, nên nút 'Kiểm tra toàn dàn' vẫn giãn đúng 2 giây một bậc (đo: 9 lệnh, các bậc 2.0 giây).
+Bỏ trống ?wait thì hành xử y như cũ — firmware bản cũ đang chạy ngoài đồng không bị ảnh hưởng (đo: trả rỗng trong 2 ms).
+Cơ chế giãn 2 giây chống sụt áp vẫn còn nguyên và VẪN nên khoe với hội đồng — chỉ là khoe ở nút 'Kiểm tra toàn dàn', đúng chỗ nó thật sự chạy.</t>
         </is>
       </c>
     </row>
